--- a/public/inputs/y04-physical-education - input.xlsx
+++ b/public/inputs/y04-physical-education - input.xlsx
@@ -444,7 +444,6 @@
           <t>Unit 1 · Moving Well</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,7 +456,6 @@
           <t>1.1 Practise, refine and consolidate a broad range of movement skills</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -470,7 +468,6 @@
           <t>1.2 Perform and be able to link together a wider variety of movement skills in short sequences</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,7 +480,6 @@
           <t>1.3 Display movement skills that demonstrate increasing control, fluency and variety</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,7 +492,6 @@
           <t>1.4 Apply movement competence with confidence in a variety of self-selected and more structured physical activities, showing the ability to respond and adapt to changing contexts and to others’ movements, responses and roles</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,7 +504,6 @@
           <t>Unit 2 · Understanding Movement</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,7 +516,6 @@
           <t>2.1 Describe own and others’ movements using some activity-specific vocabulary and be able to identify more and less effective movement</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,7 +528,6 @@
           <t>2.2 Demonstrate (through movement) and discuss understanding of language and concepts related to actions, dynamics, space and relationships</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,7 +540,6 @@
           <t>2.3 Apply success criteria to own and others’ movement performances, and discuss ideas and plans for improvement with others</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,7 +552,6 @@
           <t>2.4 Follow and understand the need for rules, apply tactics/strategies and develop variety in compositional ideas</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -574,7 +564,6 @@
           <t>Unit 3 · Moving Creatively</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,7 +576,6 @@
           <t>3.1 Show creativity and innovation in a range of individual, group, expressive, competitive and cooperative contexts</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -600,7 +588,6 @@
           <t>3.2 Investigate, select and design alternative courses of action in response to given movement and environmental challenges.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,7 +600,6 @@
           <t>3.3 Address given and self-directed tasks and challenges, finding solutions through innovative use of movement in individual and group tasks</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -626,7 +612,6 @@
           <t>3.4 Identify and demonstrate a range of compositional ideas in order to express a selected theme, mood or emotion</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -639,7 +624,6 @@
           <t>Unit 4 · Taking Part</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -652,7 +636,6 @@
           <t>4.1 Show involvement in individual work, sharing space, playing together, working in pairs, and working in small groups across a range of physical activities.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -665,7 +648,6 @@
           <t>4.2 Understand the concepts of team/group work and expectations and roles of individual team/group members.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -678,7 +660,6 @@
           <t>4.3 Demonstrate independence and collaboration in evaluating own and others’ work, setting short-term personal goals and areas for development</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -691,7 +672,6 @@
           <t>4.4 Take responsibility in leading and following the lead of others, contributing positively to the group’s tasks and activities.</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -704,7 +684,6 @@
           <t>4.5 Understand own and others’ movement strengths, areas for improvement and potential, applying this knowledge to improve movement proficiency and refine movement patterns and sequences.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -717,7 +696,6 @@
           <t>4.6 Show patience and care when working with others. Listen to others and plan together to find solutions to movement challenges</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -730,7 +708,6 @@
           <t>Unit 5 · Taking Responsibility</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -743,7 +720,6 @@
           <t>5.1 Show ability to share space and equipment skilfully and safely, communicating and collaborating with others during this process.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -756,7 +732,6 @@
           <t>5.2 Show personal responsibility in physical activities, negotiating successfully and appropriately with other learners in respect of shared equipment, space and movement ideas.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -769,7 +744,6 @@
           <t>5.3 Understand and appreciate the need for rules and regulations to foster fair play, following these in a variety of collaborative and competitive physical activities in small teams/groups.</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -782,7 +756,6 @@
           <t>5.4 Employ a range of appropriate help-seeking strategies at appropriate moments when undertaking group physical activities.</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -795,7 +768,6 @@
           <t>5.5 Offer constructive and specific feedback to others on strengths and goals. Demonstrate respect for others when they are working to improve individual/group performances</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -808,7 +780,6 @@
           <t>Unit 6 · Healthy Bodies</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -821,7 +792,6 @@
           <t>6.1 Demonstrate understanding of the importance of physical activity in relation to health, fitness and wellbeing</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -834,7 +804,6 @@
           <t>6.2 Identify which body parts, including joints and muscles, are being used during a physical activity and discuss how working these can contribute to physical fitness. Describe the different components of fitness.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -847,7 +816,6 @@
           <t>6.3 Engage in and plan for a range of physical activities, evaluating and comparing the required level of intensity within each of these.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -860,7 +828,6 @@
           <t>6.4 Undertake physical activities responsibly and safely through assessing and managing risk and appropriate preparation and learning.</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -873,7 +840,6 @@
           <t>6.5 Identify the key components of warm-up and cool-down routines in preparation for physical activity, understanding their importance.</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -886,7 +852,6 @@
           <t>6.6 Demonstrate understanding that a varied balanced diet contributes to a healthy and active lifestyle.</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -896,10 +861,9 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Test term 1, term 2 and term3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Test term 1, term 2 and term 3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
